--- a/data/4-reports/7_SNOMED_Matches_All.xlsx
+++ b/data/4-reports/7_SNOMED_Matches_All.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNOMED Matches (All)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SNOMED Matches (All)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SNOMED Matches (All)'!$A$1:$K$1</definedName>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K212"/>
+  <dimension ref="A1:K211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8873,51 +8873,75 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001168</t>
+          <t>ARI:0001169</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Primary immune deficiency</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr"/>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr"/>
+          <t>Primary sclerosing cholangitis</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>197441003</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Primary sclerosing cholangitis</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>4058821</t>
+        </is>
+      </c>
       <c r="I169" s="2" t="inlineStr"/>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>442459007, 362993009, 36138009, 31323000, 37548006</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr"/>
+          <t>197441003</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001169</t>
+          <t>ARI:0001170</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
+          <t>Progressive hemifacial atrophy</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8937,13 +8961,13 @@
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>4058821</t>
+          <t>37397558</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr"/>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>197441003</t>
+          <t>718224004</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
@@ -8955,22 +8979,22 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001170</t>
+          <t>ARI:0001171</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>9014002</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
+          <t>Psoriasis</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -8990,13 +9014,13 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>37397558</t>
+          <t>140168</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>718224004</t>
+          <t>37042000, 9014002</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
@@ -9008,22 +9032,22 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001171</t>
+          <t>ARI:0001172</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>9014002</t>
+          <t>156370009</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9043,13 +9067,13 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>140168</t>
+          <t>40319772</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>37042000, 9014002</t>
+          <t>156370009, 33339001</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
@@ -9061,22 +9085,22 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001172</t>
+          <t>ARI:0001173</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>156370009</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9096,13 +9120,13 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>40319772</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>156370009, 33339001</t>
+          <t>50715003</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
@@ -9114,22 +9138,22 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001173</t>
+          <t>ARI:0001174</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9149,13 +9173,13 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t>140065</t>
+          <t>133283</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>50715003</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -9167,22 +9191,22 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001174</t>
+          <t>ARI:0001175</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>230191005</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
+          <t>Rasmussen syndrome</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9202,13 +9226,13 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>133283</t>
+          <t>4041672</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>74578003</t>
+          <t>230191005, 435341000124104</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
@@ -9220,22 +9244,22 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001175</t>
+          <t>ARI:0001176</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>230191005</t>
+          <t>356198000</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
+          <t>Secondary Raynaud's phenomenon</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9255,13 +9279,13 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>4041672</t>
+          <t>4229162</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>230191005, 435341000124104</t>
+          <t>356198000, 266261006</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
@@ -9273,22 +9297,22 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001176</t>
+          <t>ARI:0001177</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>356198000</t>
+          <t>201736002</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9308,13 +9332,13 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>4229162</t>
+          <t>40399768</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>356198000, 266261006</t>
+          <t>201736002, 67224007</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
@@ -9326,22 +9350,22 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001177</t>
+          <t>ARI:0001178</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>201736002</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9361,13 +9385,13 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>40399768</t>
+          <t>4216873</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>201736002, 67224007</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -9379,22 +9403,22 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001178</t>
+          <t>ARI:0001179</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9414,13 +9438,13 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>4216873</t>
+          <t>73754</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
@@ -9432,22 +9456,22 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001179</t>
+          <t>ARI:0001180</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
+          <t>Retinocochleocerebral vasculopathy</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9467,13 +9491,13 @@
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>45765600</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>32914008</t>
+          <t>702575003</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
@@ -9485,27 +9509,27 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001180</t>
+          <t>ARI:0001181</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic Chorea</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic chorea</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -9520,13 +9544,13 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>45765600</t>
+          <t>444120</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>702575003</t>
+          <t>46826000</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
@@ -9538,27 +9562,27 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001181</t>
+          <t>ARI:0001182</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic Chorea</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>58718002</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic chorea</t>
+          <t>Rheumatic fever</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -9573,13 +9597,13 @@
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>444120</t>
+          <t>442313</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>46826000</t>
+          <t>58718002, 194709000</t>
         </is>
       </c>
       <c r="K182" s="5" t="inlineStr">
@@ -9591,22 +9615,22 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001182</t>
+          <t>ARI:0001183</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>58718002</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
+          <t>Rheumatoid aortitis</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9626,13 +9650,13 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>442313</t>
+          <t>4306357</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>58718002, 194709000</t>
+          <t>38877003</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
@@ -9644,22 +9668,22 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001183</t>
+          <t>ARI:0001184</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
+          <t>Rheumatoid arthritis</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -9679,13 +9703,13 @@
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>4306357</t>
+          <t>80809</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>38877003</t>
+          <t>69896004</t>
         </is>
       </c>
       <c r="K184" s="5" t="inlineStr">
@@ -9697,22 +9721,22 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001184</t>
+          <t>ARI:0001185</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
+          <t>Rheumatoid vasculitis</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -9732,13 +9756,13 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>80809</t>
+          <t>4271003</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr"/>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>69896004</t>
+          <t>400054000</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr">
@@ -9750,22 +9774,22 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001185</t>
+          <t>ARI:0001186</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>31541009</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
+          <t>Sarcoidosis</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -9785,13 +9809,13 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>4271003</t>
+          <t>438688</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>400054000</t>
+          <t>72470008, 238676008, 31541009</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
@@ -9803,22 +9827,22 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001186</t>
+          <t>ARI:0001187</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>31541009</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9838,13 +9862,13 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>438688</t>
+          <t>4297647</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>72470008, 238676008, 31541009</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="K187" s="5" t="inlineStr">
@@ -9856,22 +9880,22 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001187</t>
+          <t>ARI:0001188</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9891,13 +9915,13 @@
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>4297647</t>
+          <t>434944</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>78370002</t>
         </is>
       </c>
       <c r="K188" s="5" t="inlineStr">
@@ -9909,22 +9933,22 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001188</t>
+          <t>ARI:0001189</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Sjögren's disease</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>78370002</t>
+          <t>302896008</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9939,45 +9963,41 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>434944</t>
+          <t>4120320</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>78370002</t>
-        </is>
-      </c>
-      <c r="K189" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>83901003</t>
+        </is>
+      </c>
+      <c r="K189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001189</t>
+          <t>ARI:0001190</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Sjögren's disease</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>302896008</t>
+          <t>68815009</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9992,41 +10012,45 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t>4120320</t>
+          <t>4285717</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>83901003</t>
-        </is>
-      </c>
-      <c r="K190" s="2" t="inlineStr"/>
+          <t>68815009</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001190</t>
+          <t>ARI:0001191</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10046,13 +10070,13 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>4285717</t>
+          <t>46271378</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr"/>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>68815009</t>
+          <t>709489006</t>
         </is>
       </c>
       <c r="K191" s="5" t="inlineStr">
@@ -10064,22 +10088,22 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001191</t>
+          <t>ARI:0001192</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10099,13 +10123,13 @@
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
-          <t>46271378</t>
+          <t>36674282</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>709489006</t>
+          <t>771271000</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
@@ -10117,22 +10141,22 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001192</t>
+          <t>ARI:0001193</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+          <t>Stiff-person syndrome</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10152,13 +10176,13 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>36674282</t>
+          <t>379008</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>771271000</t>
+          <t>5217008</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr">
@@ -10170,22 +10194,22 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001193</t>
+          <t>ARI:0001194</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10205,13 +10229,13 @@
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>379008</t>
+          <t>4249899</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>73774007</t>
         </is>
       </c>
       <c r="K194" s="5" t="inlineStr">
@@ -10223,22 +10247,22 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001194</t>
+          <t>ARI:0001195</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10258,13 +10282,13 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>4249899</t>
+          <t>438739</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>73774007</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
@@ -10276,22 +10300,22 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001195</t>
+          <t>ARI:0001196</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10311,13 +10335,13 @@
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
-          <t>438739</t>
+          <t>257628</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>55464009</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr">
@@ -10329,22 +10353,22 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001196</t>
+          <t>ARI:0001197</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
+          <t>Systemic mast cell disease</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10364,13 +10388,13 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>257628</t>
+          <t>4246284</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>55464009</t>
+          <t>397016004</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr">
@@ -10382,22 +10406,22 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001197</t>
+          <t>ARI:0001198</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
+          <t>Systemic sclerosis</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10417,13 +10441,13 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>4246284</t>
+          <t>134442</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr"/>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>397016004</t>
+          <t>89155008</t>
         </is>
       </c>
       <c r="K198" s="5" t="inlineStr">
@@ -10435,22 +10459,22 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001198</t>
+          <t>ARI:0001199</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>298285004</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10470,13 +10494,13 @@
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>134442</t>
+          <t>4185187</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>298285004, 31848007, 128461001</t>
         </is>
       </c>
       <c r="K199" s="5" t="inlineStr">
@@ -10488,22 +10512,22 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001199</t>
+          <t>ARI:0001200</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's arteritis</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>298285004</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10518,18 +10542,18 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Takayasu's disease</t>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t>4185187</t>
+          <t>440740</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>298285004, 31848007, 128461001</t>
+          <t>359789008</t>
         </is>
       </c>
       <c r="K200" s="5" t="inlineStr">
@@ -10541,22 +10565,22 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001200</t>
+          <t>ARI:0001201</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's arteritis</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10571,18 +10595,18 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's disease</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>440740</t>
+          <t>4290976</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>359789008</t>
+          <t>400130008</t>
         </is>
       </c>
       <c r="K201" s="5" t="inlineStr">
@@ -10594,110 +10618,110 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001201</t>
+          <t>ARI:0001202</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>400130008</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>TIF1-gamma positive dermatomyositis</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr"/>
+      <c r="D202" s="3" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr">
-        <is>
-          <t>4290976</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr"/>
-      <c r="J202" s="3" t="inlineStr">
-        <is>
-          <t>400130008</t>
-        </is>
-      </c>
-      <c r="K202" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="J202" s="3" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001202</t>
+          <t>ARI:0001203</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>TIF1-gamma positive dermatomyositis</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr"/>
-      <c r="D203" s="3" t="inlineStr"/>
-      <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr"/>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>95794005</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>4317989</t>
+        </is>
+      </c>
       <c r="I203" s="2" t="inlineStr"/>
-      <c r="J203" s="3" t="inlineStr"/>
-      <c r="K203" s="2" t="inlineStr"/>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>95794005</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001203</t>
+          <t>ARI:0001204</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelitis</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>95794005</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelopathy syndrome</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -10707,13 +10731,13 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>4317989</t>
+          <t>443904</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>95794005</t>
+          <t>16631009</t>
         </is>
       </c>
       <c r="K204" s="5" t="inlineStr">
@@ -10725,32 +10749,32 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001204</t>
+          <t>ARI:0001205</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelitis</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelopathy syndrome</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -10760,13 +10784,13 @@
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>443904</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>16631009</t>
+          <t>64766004</t>
         </is>
       </c>
       <c r="K205" s="5" t="inlineStr">
@@ -10778,22 +10802,22 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001205</t>
+          <t>ARI:0001206</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Undifferentiated connective tissue disease</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>239918008</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
+          <t>Undifferentiated connective tissue disease</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10813,13 +10837,13 @@
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>81893</t>
+          <t>4344165</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>64766004</t>
+          <t>239918008</t>
         </is>
       </c>
       <c r="K206" s="5" t="inlineStr">
@@ -10831,104 +10855,104 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001206</t>
+          <t>ARI:0001207</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Undifferentiated connective tissue disease</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>239918008</t>
-        </is>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>Undifferentiated connective tissue disease</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Urticarial vasculitis</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr"/>
+      <c r="D207" s="3" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr">
-        <is>
-          <t>4344165</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr"/>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>239918008</t>
-        </is>
-      </c>
-      <c r="K207" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>402656007</t>
+        </is>
+      </c>
+      <c r="K207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001207</t>
+          <t>ARI:0001208</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Urticarial vasculitis</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr"/>
-      <c r="D208" s="3" t="inlineStr"/>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>128473001</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>4028363</t>
+        </is>
+      </c>
       <c r="I208" s="2" t="inlineStr"/>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>402656007</t>
-        </is>
-      </c>
-      <c r="K208" s="2" t="inlineStr"/>
+          <t>128473001, 231947004</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001208</t>
+          <t>ARI:0001209</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>128473001</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10948,13 +10972,13 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>4028363</t>
+          <t>138502</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>128473001, 231947004</t>
+          <t>56727007</t>
         </is>
       </c>
       <c r="K209" s="5" t="inlineStr">
@@ -10966,22 +10990,22 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001209</t>
+          <t>ARI:0001210</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>56727007</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11001,13 +11025,13 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>138502</t>
+          <t>4108968</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>56727007</t>
+          <t>193497004</t>
         </is>
       </c>
       <c r="K210" s="5" t="inlineStr">
@@ -11019,22 +11043,22 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001210</t>
+          <t>ARI:0001211</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
+          <t>Warm autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>193497004</t>
+          <t>3978000</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
+          <t>Warm autoimmune hemolytic anemia</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11054,69 +11078,16 @@
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>4108968</t>
+          <t>4219853</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>193497004</t>
+          <t>3978000</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001211</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>3978000</t>
-        </is>
-      </c>
-      <c r="D212" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="inlineStr">
-        <is>
-          <t>4219853</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr"/>
-      <c r="J212" s="3" t="inlineStr">
-        <is>
-          <t>3978000</t>
-        </is>
-      </c>
-      <c r="K212" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -11421,88 +11392,88 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId378"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
